--- a/demo/input_template.xlsx
+++ b/demo/input_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOFKV\PycharmProjects\proseqteleporter\demo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GOFKV\PycharmProjects\seqTeleporter\demo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB22FCC-A2EC-46FB-AEB9-982B15DA38A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C45B2-6206-4085-B09D-714D79C081AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="768" activeTab="5" xr2:uid="{92EDD624-EB72-41A1-9013-2A2A4F6AE6A6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="926" activeTab="3" xr2:uid="{92EDD624-EB72-41A1-9013-2A2A4F6AE6A6}"/>
   </bookViews>
   <sheets>
     <sheet name="parameter_guide" sheetId="2" r:id="rId1"/>
